--- a/src/classifications/rajesh_test.xlsx
+++ b/src/classifications/rajesh_test.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wavicledata-my.sharepoint.com/personal/rajesh_puchakayala_wavicledata_com/Documents/Desktop/project/perview/classifications/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wavicledata-my.sharepoint.com/personal/rajesh_puchakayala_wavicledata_com/Documents/Desktop/project/perview/src/classifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="18" documentId="11_71F24F94407219B5A74575F6183D3E4314525CC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FAA22FC-9400-42E8-AF4B-6202CEBD0975}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="14927" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="14927" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SQL Server" sheetId="1" r:id="rId1"/>
